--- a/frontend/app testing/load_test_results.xlsx
+++ b/frontend/app testing/load_test_results.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>877.15</v>
+        <v>216.86</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>303.52</v>
+        <v>130.73</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>794.5</v>
+        <v>610.6799999999999</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>864.42</v>
+        <v>696.24</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -808,7 +808,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>535.36</v>
+        <v>326.87</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>826.08</v>
+        <v>939.21</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -910,7 +910,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>506.89</v>
+        <v>853.3200000000001</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>447.33</v>
+        <v>503.24</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>183.62</v>
+        <v>668.45</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>801.08</v>
+        <v>373.77</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>316.51</v>
+        <v>742.25</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>904.79</v>
+        <v>214.37</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>185.71</v>
+        <v>849.01</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>498.6</v>
+        <v>183.26</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1318,7 +1318,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>155.32</v>
+        <v>745.15</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>812.83</v>
+        <v>481.73</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>543.4299999999999</v>
+        <v>543.4</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>823.62</v>
+        <v>689.28</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>443.88</v>
+        <v>364.67</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>210.64</v>
+        <v>467.76</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1624,7 +1624,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>763.0599999999999</v>
+        <v>432.41</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>826.11</v>
+        <v>529.66</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>867.23</v>
+        <v>443.91</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>584.49</v>
+        <v>267.61</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1828,7 +1828,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>803.91</v>
+        <v>312.96</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>492.79</v>
+        <v>460.88</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1930,7 +1930,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>926.6</v>
+        <v>147.96</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>513.09</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>729.39</v>
+        <v>909.8200000000001</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>861.63</v>
+        <v>173.86</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>548.5700000000001</v>
+        <v>710.2</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>819.1900000000001</v>
+        <v>910.04</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -2236,7 +2236,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>477.79</v>
+        <v>325.51</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>622.59</v>
+        <v>934.37</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2338,7 +2338,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>818.16</v>
+        <v>434</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>197.11</v>
+        <v>696.77</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>767.91</v>
+        <v>556.8099999999999</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>798.95</v>
+        <v>216.07</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2542,7 +2542,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>509.23</v>
+        <v>431.57</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>586.71</v>
+        <v>679.55</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2644,7 +2644,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>944.6799999999999</v>
+        <v>747.64</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>642.48</v>
+        <v>229.31</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>813.54</v>
+        <v>265.66</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>855.29</v>
+        <v>572.08</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2848,7 +2848,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>540.49</v>
+        <v>533.52</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>678.71</v>
+        <v>153.6</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>293.36</v>
+        <v>203.12</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>829.21</v>
+        <v>864.49</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>922.66</v>
+        <v>914.4400000000001</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>599.86</v>
+        <v>467.69</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -3154,7 +3154,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>821.64</v>
+        <v>282.67</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>368.2</v>
+        <v>645.09</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -3256,7 +3256,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>234.85</v>
+        <v>530.96</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>631.53</v>
+        <v>527.05</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>184.96</v>
+        <v>422.72</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>725.42</v>
+        <v>603.36</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>604.65</v>
+        <v>398.59</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>596.8200000000001</v>
+        <v>744.52</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3562,7 +3562,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>789.58</v>
+        <v>227.4</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>140.94</v>
+        <v>254.92</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3695,11 +3695,11 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>297.8</v>
+        <v>883.67</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>14.31 req/s</t>
+          <t>2.65 req/s</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3746,16 +3746,16 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>313.99</v>
+        <v>122.04</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>8.68 req/s</t>
+          <t>11.21 req/s</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -3766,7 +3766,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3797,11 +3797,11 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>414.48</v>
+        <v>608.16</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>11.71 req/s</t>
+          <t>4.43 req/s</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3848,16 +3848,16 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>863.72</v>
+        <v>545.21</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>12.11 req/s</t>
+          <t>4.52 req/s</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3868,7 +3868,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3899,16 +3899,16 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>419.18</v>
+        <v>626.73</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>12.54 req/s</t>
+          <t>6.2 req/s</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -3950,16 +3950,16 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>789.4</v>
+        <v>699.65</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>8.88 req/s</t>
+          <t>10.16 req/s</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4001,11 +4001,11 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>651.9</v>
+        <v>906.16</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>11.52 req/s</t>
+          <t>7.68 req/s</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4052,16 +4052,16 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>313.62</v>
+        <v>211.57</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>4.22 req/s</t>
+          <t>7.86 req/s</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -4072,7 +4072,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4103,11 +4103,11 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>208.62</v>
+        <v>563.09</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>9.46 req/s</t>
+          <t>1.3 req/s</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4154,16 +4154,16 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>892.04</v>
+        <v>743.95</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>4.82 req/s</t>
+          <t>10.46 req/s</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -4174,7 +4174,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4205,16 +4205,16 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>602.66</v>
+        <v>838.84</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>7.25 req/s</t>
+          <t>4.88 req/s</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4256,16 +4256,16 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>427.68</v>
+        <v>390.86</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>6.06 req/s</t>
+          <t>10.0 req/s</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -4276,7 +4276,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4307,16 +4307,16 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>741.42</v>
+        <v>310.21</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>11.29 req/s</t>
+          <t>3.78 req/s</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4358,16 +4358,16 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>899.54</v>
+        <v>877.51</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>14.24 req/s</t>
+          <t>5.23 req/s</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -4378,7 +4378,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4409,16 +4409,16 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>450.85</v>
+        <v>838.46</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>5.68 req/s</t>
+          <t>7.57 req/s</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4460,16 +4460,16 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>501.61</v>
+        <v>591.01</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>8.09 req/s</t>
+          <t>8.7 req/s</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4480,7 +4480,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4511,11 +4511,11 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>704.97</v>
+        <v>572.6900000000001</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>6.77 req/s</t>
+          <t>12.88 req/s</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4562,16 +4562,16 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>749.03</v>
+        <v>190.01</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>3.43 req/s</t>
+          <t>4.23 req/s</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4582,7 +4582,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>628.61</v>
+        <v>780.6</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>12.46 req/s</t>
+          <t>6.95 req/s</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4664,16 +4664,16 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>875.9299999999999</v>
+        <v>704.63</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>3.48 req/s</t>
+          <t>11.83 req/s</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4684,7 +4684,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4715,11 +4715,11 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>489.95</v>
+        <v>904.85</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>7.25 req/s</t>
+          <t>7.57 req/s</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>890.26</v>
+        <v>123.78</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>1.57 req/s</t>
+          <t>8.29 req/s</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4817,16 +4817,16 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>248.92</v>
+        <v>714.08</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>2.03 req/s</t>
+          <t>8.15 req/s</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4868,16 +4868,16 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>936.54</v>
+        <v>145.8</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>8.05 req/s</t>
+          <t>6.92 req/s</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4888,7 +4888,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4919,16 +4919,16 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>898.39</v>
+        <v>693.63</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>12.93 req/s</t>
+          <t>12.35 req/s</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>862.29</v>
+        <v>298.31</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>12.28 req/s</t>
+          <t>3.07 req/s</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
@@ -4990,7 +4990,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5021,11 +5021,11 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>784.6900000000001</v>
+        <v>739.64</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>6.23 req/s</t>
+          <t>6.11 req/s</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5072,16 +5072,16 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>679.05</v>
+        <v>262.58</v>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>4.74 req/s</t>
+          <t>11.94 req/s</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
@@ -5092,7 +5092,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5123,11 +5123,11 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>605.4400000000001</v>
+        <v>929.6799999999999</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>5.21 req/s</t>
+          <t>3.3 req/s</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5174,16 +5174,16 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>318.26</v>
+        <v>354.12</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>3.65 req/s</t>
+          <t>14.42 req/s</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -5194,7 +5194,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>894.6900000000001</v>
+        <v>471</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>712.54</v>
+        <v>708.8</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -5296,7 +5296,7 @@
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>785.39</v>
+        <v>518.1799999999999</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>504.71</v>
+        <v>148.25</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -5398,7 +5398,7 @@
       <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>431.53</v>
+        <v>785.6</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>511.2</v>
+        <v>492.3</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5500,7 +5500,7 @@
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>860.84</v>
+        <v>829.99</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>412.17</v>
+        <v>771.83</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
@@ -5602,7 +5602,7 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>618.1900000000001</v>
+        <v>347.19</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5653,7 +5653,7 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>674.45</v>
+        <v>710.9299999999999</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -5704,7 +5704,7 @@
       <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>400.78</v>
+        <v>394.54</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5755,7 +5755,7 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>357.03</v>
+        <v>273.97</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>245.55</v>
+        <v>408.79</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>372.37</v>
+        <v>338.95</v>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
       <c r="J105" s="4" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>882.8099999999999</v>
+        <v>693.6799999999999</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>174.75</v>
+        <v>444.29</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -6010,7 +6010,7 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>600.61</v>
+        <v>382.05</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>668.38</v>
+        <v>398.33</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -6112,7 +6112,7 @@
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>264.62</v>
+        <v>188.34</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>190.99</v>
+        <v>871.98</v>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -6214,7 +6214,7 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>373.28</v>
+        <v>828.8</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>578.83</v>
+        <v>476.23</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
       <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>640.16</v>
+        <v>330.94</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>217.66</v>
+        <v>715.66</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -6418,7 +6418,7 @@
       <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>789.39</v>
+        <v>890.13</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>285.86</v>
+        <v>140.17</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -6520,7 +6520,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>502.24</v>
+        <v>441.49</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>558.85</v>
+        <v>915.58</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -6622,7 +6622,7 @@
       <c r="J119" s="4" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>438.14</v>
+        <v>392.3</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>948.85</v>
+        <v>588.4</v>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>291.56</v>
+        <v>796.46</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>742.46</v>
+        <v>166.73</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -6826,7 +6826,7 @@
       <c r="J123" s="4" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>303.88</v>
+        <v>122.37</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -6877,7 +6877,7 @@
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>499.34</v>
+        <v>247.33</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -6928,7 +6928,7 @@
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>240.09</v>
+        <v>668.9</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>549.01</v>
+        <v>135.05</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
@@ -7030,7 +7030,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>467.7</v>
+        <v>884.96</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>143.69</v>
+        <v>135.04</v>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
@@ -7132,7 +7132,7 @@
       <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>365.21</v>
+        <v>530.67</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>476.19</v>
+        <v>141.92</v>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -7234,7 +7234,7 @@
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>691.71</v>
+        <v>865.1799999999999</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>331.53</v>
+        <v>411.82</v>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
@@ -7336,7 +7336,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>494.26</v>
+        <v>753.5</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>529.8200000000001</v>
+        <v>856.1</v>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>481.4</v>
+        <v>431.11</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>132.88</v>
+        <v>339.99</v>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -7540,7 +7540,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>850.27</v>
+        <v>867.64</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>761.16</v>
+        <v>446.19</v>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
@@ -7642,7 +7642,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>667.6900000000001</v>
+        <v>240.62</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>782.73</v>
+        <v>691.64</v>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
@@ -7744,7 +7744,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>790.58</v>
+        <v>413.58</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -7795,7 +7795,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>875.08</v>
+        <v>658.03</v>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7846,7 +7846,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>813.79</v>
+        <v>883.3</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>243.9</v>
+        <v>225.78</v>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -7948,7 +7948,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7979,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>493.21</v>
+        <v>607.42</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>270.73</v>
+        <v>889.54</v>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
@@ -8050,7 +8050,7 @@
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>192.94</v>
+        <v>754.59</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>565.9</v>
+        <v>404.34</v>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
@@ -8152,7 +8152,7 @@
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>536.17</v>
+        <v>837.41</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>455.79</v>
+        <v>353.38</v>
       </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
@@ -8254,7 +8254,7 @@
       <c r="J151" s="4" t="inlineStr"/>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>601.22</v>
+        <v>633.3099999999999</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>740</v>
+        <v>895.78</v>
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
@@ -8356,7 +8356,7 @@
       <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>185.03</v>
+        <v>941.72</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -8407,7 +8407,7 @@
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>726.2</v>
+        <v>321.34</v>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
@@ -8458,7 +8458,7 @@
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>693.9400000000001</v>
+        <v>608.8200000000001</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>725.8200000000001</v>
+        <v>901.8</v>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -8560,7 +8560,7 @@
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>133.48</v>
+        <v>488.63</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>387.87</v>
+        <v>638.49</v>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
@@ -8662,7 +8662,7 @@
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>668.4400000000001</v>
+        <v>439.85</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>211.74</v>
+        <v>293.38</v>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
@@ -8764,7 +8764,7 @@
       <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>873.91</v>
+        <v>718.26</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>544.89</v>
+        <v>742.3099999999999</v>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -8866,7 +8866,7 @@
       <c r="J163" s="4" t="inlineStr"/>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>534.41</v>
+        <v>121.06</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="F165" s="4" t="n">
-        <v>362.85</v>
+        <v>208.13</v>
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
@@ -8968,7 +8968,7 @@
       <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>325.26</v>
+        <v>376.96</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>212.13</v>
+        <v>543.09</v>
       </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
@@ -9070,7 +9070,7 @@
       <c r="J167" s="4" t="inlineStr"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>232.95</v>
+        <v>806.16</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>348.24</v>
+        <v>270.01</v>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
@@ -9172,7 +9172,7 @@
       <c r="J169" s="4" t="inlineStr"/>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>803.35</v>
+        <v>336.62</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>888.21</v>
+        <v>421.54</v>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="J171" s="4" t="inlineStr"/>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>649.15</v>
+        <v>147.09</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -9325,7 +9325,7 @@
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>923.3099999999999</v>
+        <v>797.36</v>
       </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
       <c r="J173" s="4" t="inlineStr"/>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>907.52</v>
+        <v>180.73</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>393.11</v>
+        <v>460.07</v>
       </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
@@ -9478,7 +9478,7 @@
       <c r="J175" s="4" t="inlineStr"/>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>791.21</v>
+        <v>131.41</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>782.9400000000001</v>
+        <v>362.01</v>
       </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
@@ -9580,7 +9580,7 @@
       <c r="J177" s="4" t="inlineStr"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>195.33</v>
+        <v>248</v>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -9631,7 +9631,7 @@
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>540.96</v>
+        <v>860.05</v>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -9682,7 +9682,7 @@
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>206.88</v>
+        <v>183.31</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -9733,7 +9733,7 @@
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>186.31</v>
+        <v>376.84</v>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -9784,7 +9784,7 @@
       <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9815,16 +9815,16 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>501.55</v>
+        <v>805.11</v>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>4.36 req/s</t>
+          <t>9.05 req/s</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9866,16 +9866,16 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>194.44</v>
+        <v>183.47</v>
       </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
-          <t>2.95 req/s</t>
+          <t>9.85 req/s</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
@@ -9886,7 +9886,7 @@
       <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9917,16 +9917,16 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>627.3200000000001</v>
+        <v>264.87</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>9.88 req/s</t>
+          <t>4.47 req/s</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -9968,16 +9968,16 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>866.12</v>
+        <v>938.75</v>
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>7.46 req/s</t>
+          <t>2.19 req/s</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
@@ -9988,7 +9988,7 @@
       <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10019,11 +10019,11 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>713.83</v>
+        <v>184.04</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>6.83 req/s</t>
+          <t>11.15 req/s</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -10039,7 +10039,7 @@
       <c r="J186" s="2" t="inlineStr"/>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10070,16 +10070,16 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>339.02</v>
+        <v>431.75</v>
       </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>7.39 req/s</t>
+          <t>4.79 req/s</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -10090,7 +10090,7 @@
       <c r="J187" s="4" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10121,16 +10121,16 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>772.53</v>
+        <v>489.98</v>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>10.43 req/s</t>
+          <t>2.59 req/s</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10172,16 +10172,16 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>151.15</v>
+        <v>885.35</v>
       </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
-          <t>1.68 req/s</t>
+          <t>9.47 req/s</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
@@ -10192,7 +10192,7 @@
       <c r="J189" s="4" t="inlineStr"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10223,16 +10223,16 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>935.5700000000001</v>
+        <v>723.29</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>9.69 req/s</t>
+          <t>3.34 req/s</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10274,16 +10274,16 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>532.09</v>
+        <v>935.52</v>
       </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
-          <t>4.72 req/s</t>
+          <t>4.79 req/s</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
@@ -10294,7 +10294,7 @@
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10325,16 +10325,16 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>812.27</v>
+        <v>854.0700000000001</v>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>10.97 req/s</t>
+          <t>1.41 req/s</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10376,16 +10376,16 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>611.6</v>
+        <v>688.72</v>
       </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
-          <t>7.8 req/s</t>
+          <t>12.48 req/s</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I193" s="4" t="inlineStr">
@@ -10396,7 +10396,7 @@
       <c r="J193" s="4" t="inlineStr"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10427,16 +10427,16 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>553.91</v>
+        <v>874.84</v>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>6.51 req/s</t>
+          <t>8.74 req/s</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -10447,7 +10447,7 @@
       <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10478,16 +10478,16 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>427.28</v>
+        <v>337.2</v>
       </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
-          <t>2.97 req/s</t>
+          <t>14.45 req/s</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I195" s="4" t="inlineStr">
@@ -10498,7 +10498,7 @@
       <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10529,16 +10529,16 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>824.74</v>
+        <v>593.51</v>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>12.8 req/s</t>
+          <t>4.06 req/s</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -10549,7 +10549,7 @@
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10580,16 +10580,16 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>201.11</v>
+        <v>731.27</v>
       </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
-          <t>6.55 req/s</t>
+          <t>9.22 req/s</t>
         </is>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
@@ -10600,7 +10600,7 @@
       <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10631,16 +10631,16 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>289.99</v>
+        <v>176.95</v>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>6.14 req/s</t>
+          <t>11.92 req/s</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10651,7 +10651,7 @@
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10682,16 +10682,16 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>529.9299999999999</v>
+        <v>203.29</v>
       </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>10.11 req/s</t>
+          <t>2.53 req/s</t>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I199" s="4" t="inlineStr">
@@ -10702,7 +10702,7 @@
       <c r="J199" s="4" t="inlineStr"/>
       <c r="K199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10733,16 +10733,16 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>137.25</v>
+        <v>558.7</v>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>8.69 req/s</t>
+          <t>1.25 req/s</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -10753,7 +10753,7 @@
       <c r="J200" s="2" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10784,16 +10784,16 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>860.79</v>
+        <v>130.74</v>
       </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
-          <t>7.18 req/s</t>
+          <t>10.78 req/s</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I201" s="4" t="inlineStr">
@@ -10804,7 +10804,7 @@
       <c r="J201" s="4" t="inlineStr"/>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10835,16 +10835,16 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>722.87</v>
+        <v>560.05</v>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>10.1 req/s</t>
+          <t>4.1 req/s</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10886,16 +10886,16 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>915.04</v>
+        <v>724.86</v>
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>12.73 req/s</t>
+          <t>10.72 req/s</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I203" s="4" t="inlineStr">
@@ -10906,7 +10906,7 @@
       <c r="J203" s="4" t="inlineStr"/>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10937,11 +10937,11 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>268.22</v>
+        <v>437.62</v>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>12.02 req/s</t>
+          <t>2.7 req/s</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -10988,16 +10988,16 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>207.87</v>
+        <v>683.05</v>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>6.85 req/s</t>
+          <t>12.59 req/s</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I205" s="4" t="inlineStr">
@@ -11008,7 +11008,7 @@
       <c r="J205" s="4" t="inlineStr"/>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>822.53</v>
+        <v>136.74</v>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>8.03 req/s</t>
+          <t>11.9 req/s</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       <c r="J206" s="2" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11090,16 +11090,16 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>230.97</v>
+        <v>759.49</v>
       </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
-          <t>11.16 req/s</t>
+          <t>12.44 req/s</t>
         </is>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I207" s="4" t="inlineStr">
@@ -11110,7 +11110,7 @@
       <c r="J207" s="4" t="inlineStr"/>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11141,16 +11141,16 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>306.65</v>
+        <v>613.88</v>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>8.28 req/s</t>
+          <t>14.06 req/s</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
@@ -11161,7 +11161,7 @@
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11192,16 +11192,16 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>682.97</v>
+        <v>846.45</v>
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>12.08 req/s</t>
+          <t>13.03 req/s</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I209" s="4" t="inlineStr">
@@ -11212,7 +11212,7 @@
       <c r="J209" s="4" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11243,16 +11243,16 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>858.16</v>
+        <v>623.46</v>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>12.53 req/s</t>
+          <t>8.25 req/s</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
@@ -11263,7 +11263,7 @@
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11294,16 +11294,16 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>916.37</v>
+        <v>800.73</v>
       </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
-          <t>12.99 req/s</t>
+          <t>7.12 req/s</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I211" s="4" t="inlineStr">
@@ -11314,7 +11314,7 @@
       <c r="J211" s="4" t="inlineStr"/>
       <c r="K211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>713.5700000000001</v>
+        <v>635.08</v>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
@@ -11365,7 +11365,7 @@
       <c r="J212" s="2" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>677.28</v>
+        <v>718.5</v>
       </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
       <c r="J213" s="4" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11447,7 +11447,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>274.53</v>
+        <v>494.91</v>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
@@ -11467,7 +11467,7 @@
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>234.43</v>
+        <v>247.05</v>
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr">
@@ -11518,7 +11518,7 @@
       <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>358.88</v>
+        <v>722.72</v>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>578.01</v>
+        <v>363.56</v>
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I217" s="4" t="inlineStr">
@@ -11620,7 +11620,7 @@
       <c r="J217" s="4" t="inlineStr"/>
       <c r="K217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>429.22</v>
+        <v>783.77</v>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -11671,7 +11671,7 @@
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>525.4299999999999</v>
+        <v>640.11</v>
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr">
@@ -11722,7 +11722,7 @@
       <c r="J219" s="4" t="inlineStr"/>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>441.95</v>
+        <v>283.73</v>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
       <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="F221" s="4" t="n">
-        <v>535.6</v>
+        <v>681.89</v>
       </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
       <c r="J221" s="4" t="inlineStr"/>
       <c r="K221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>515.88</v>
+        <v>439.64</v>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="F223" s="4" t="n">
-        <v>387.87</v>
+        <v>734.08</v>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr">
@@ -11926,7 +11926,7 @@
       <c r="J223" s="4" t="inlineStr"/>
       <c r="K223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>852.61</v>
+        <v>375.71</v>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       <c r="J224" s="2" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
         </is>
       </c>
       <c r="F225" s="4" t="n">
-        <v>436.91</v>
+        <v>555.3200000000001</v>
       </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr">
@@ -12028,7 +12028,7 @@
       <c r="J225" s="4" t="inlineStr"/>
       <c r="K225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>492.57</v>
+        <v>541.65</v>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -12079,7 +12079,7 @@
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="F227" s="4" t="n">
-        <v>560.99</v>
+        <v>213.64</v>
       </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I227" s="4" t="inlineStr">
@@ -12130,7 +12130,7 @@
       <c r="J227" s="4" t="inlineStr"/>
       <c r="K227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>910.45</v>
+        <v>639.17</v>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
@@ -12181,7 +12181,7 @@
       <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="F229" s="4" t="n">
-        <v>154.76</v>
+        <v>594.12</v>
       </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I229" s="4" t="inlineStr">
@@ -12232,7 +12232,7 @@
       <c r="J229" s="4" t="inlineStr"/>
       <c r="K229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>898.89</v>
+        <v>508.62</v>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
       <c r="J230" s="2" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="F231" s="4" t="n">
-        <v>692.65</v>
+        <v>778.74</v>
       </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
@@ -12334,7 +12334,7 @@
       <c r="J231" s="4" t="inlineStr"/>
       <c r="K231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12365,7 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>399.89</v>
+        <v>884.84</v>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
@@ -12385,7 +12385,7 @@
       <c r="J232" s="2" t="inlineStr"/>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="F233" s="4" t="n">
-        <v>396.34</v>
+        <v>487.93</v>
       </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I233" s="4" t="inlineStr">
@@ -12436,7 +12436,7 @@
       <c r="J233" s="4" t="inlineStr"/>
       <c r="K233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>742.08</v>
+        <v>181.68</v>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
@@ -12487,7 +12487,7 @@
       <c r="J234" s="2" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12518,7 +12518,7 @@
         </is>
       </c>
       <c r="F235" s="4" t="n">
-        <v>555.45</v>
+        <v>640.33</v>
       </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I235" s="4" t="inlineStr">
@@ -12538,7 +12538,7 @@
       <c r="J235" s="4" t="inlineStr"/>
       <c r="K235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>412.01</v>
+        <v>198.06</v>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
@@ -12589,7 +12589,7 @@
       <c r="J236" s="2" t="inlineStr"/>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12620,7 @@
         </is>
       </c>
       <c r="F237" s="4" t="n">
-        <v>519.83</v>
+        <v>928.67</v>
       </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr">
@@ -12640,7 +12640,7 @@
       <c r="J237" s="4" t="inlineStr"/>
       <c r="K237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>170.86</v>
+        <v>781.4400000000001</v>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
@@ -12691,7 +12691,7 @@
       <c r="J238" s="2" t="inlineStr"/>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
         </is>
       </c>
       <c r="F239" s="4" t="n">
-        <v>137.79</v>
+        <v>156.49</v>
       </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I239" s="4" t="inlineStr">
@@ -12742,7 +12742,7 @@
       <c r="J239" s="4" t="inlineStr"/>
       <c r="K239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="F240" s="2" t="n">
-        <v>159.79</v>
+        <v>732.29</v>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       <c r="J240" s="2" t="inlineStr"/>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="F241" s="4" t="n">
-        <v>290.36</v>
+        <v>367.42</v>
       </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I241" s="4" t="inlineStr">
@@ -12844,7 +12844,7 @@
       <c r="J241" s="4" t="inlineStr"/>
       <c r="K241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12875,7 +12875,7 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>813.47</v>
+        <v>852.15</v>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
       <c r="J242" s="2" t="inlineStr"/>
       <c r="K242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="F243" s="4" t="n">
-        <v>517.33</v>
+        <v>569.3200000000001</v>
       </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I243" s="4" t="inlineStr">
@@ -12946,7 +12946,7 @@
       <c r="J243" s="4" t="inlineStr"/>
       <c r="K243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>330.51</v>
+        <v>322.9</v>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -12997,7 +12997,7 @@
       <c r="J244" s="2" t="inlineStr"/>
       <c r="K244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="F245" s="4" t="n">
-        <v>534.36</v>
+        <v>711.72</v>
       </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
       <c r="J245" s="4" t="inlineStr"/>
       <c r="K245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>814.03</v>
+        <v>789.86</v>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -13099,7 +13099,7 @@
       <c r="J246" s="2" t="inlineStr"/>
       <c r="K246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13130,7 @@
         </is>
       </c>
       <c r="F247" s="4" t="n">
-        <v>651.29</v>
+        <v>362.75</v>
       </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I247" s="4" t="inlineStr">
@@ -13150,7 +13150,7 @@
       <c r="J247" s="4" t="inlineStr"/>
       <c r="K247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>219.52</v>
+        <v>804.39</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
@@ -13201,7 +13201,7 @@
       <c r="J248" s="2" t="inlineStr"/>
       <c r="K248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="F249" s="4" t="n">
-        <v>334.15</v>
+        <v>421.02</v>
       </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr">
@@ -13252,7 +13252,7 @@
       <c r="J249" s="4" t="inlineStr"/>
       <c r="K249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13283,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>825.6900000000001</v>
+        <v>267.19</v>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       <c r="J250" s="2" t="inlineStr"/>
       <c r="K250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
         </is>
       </c>
       <c r="F251" s="4" t="n">
-        <v>821.29</v>
+        <v>135.8</v>
       </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I251" s="4" t="inlineStr">
@@ -13354,7 +13354,7 @@
       <c r="J251" s="4" t="inlineStr"/>
       <c r="K251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>945.23</v>
+        <v>414.14</v>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
@@ -13405,7 +13405,7 @@
       <c r="J252" s="2" t="inlineStr"/>
       <c r="K252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="F253" s="4" t="n">
-        <v>393.96</v>
+        <v>249.89</v>
       </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr">
@@ -13456,7 +13456,7 @@
       <c r="J253" s="4" t="inlineStr"/>
       <c r="K253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>630.4</v>
+        <v>550.87</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
@@ -13507,7 +13507,7 @@
       <c r="J254" s="2" t="inlineStr"/>
       <c r="K254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
         </is>
       </c>
       <c r="F255" s="4" t="n">
-        <v>905.13</v>
+        <v>542.88</v>
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr">
@@ -13558,7 +13558,7 @@
       <c r="J255" s="4" t="inlineStr"/>
       <c r="K255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13589,7 +13589,7 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>306.87</v>
+        <v>925.5599999999999</v>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
@@ -13609,7 +13609,7 @@
       <c r="J256" s="2" t="inlineStr"/>
       <c r="K256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="F257" s="4" t="n">
-        <v>704.0599999999999</v>
+        <v>345.13</v>
       </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I257" s="4" t="inlineStr">
@@ -13660,7 +13660,7 @@
       <c r="J257" s="4" t="inlineStr"/>
       <c r="K257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>189.79</v>
+        <v>853.3200000000001</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
       <c r="J258" s="2" t="inlineStr"/>
       <c r="K258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
         </is>
       </c>
       <c r="F259" s="4" t="n">
-        <v>839.6</v>
+        <v>446.32</v>
       </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
       <c r="J259" s="4" t="inlineStr"/>
       <c r="K259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>315.64</v>
+        <v>548.12</v>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
@@ -13813,7 +13813,7 @@
       <c r="J260" s="2" t="inlineStr"/>
       <c r="K260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="F261" s="4" t="n">
-        <v>597.79</v>
+        <v>851.8200000000001</v>
       </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I261" s="4" t="inlineStr">
@@ -13864,7 +13864,7 @@
       <c r="J261" s="4" t="inlineStr"/>
       <c r="K261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>334.8</v>
+        <v>246.03</v>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
@@ -13915,7 +13915,7 @@
       <c r="J262" s="2" t="inlineStr"/>
       <c r="K262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="F263" s="4" t="n">
-        <v>371.32</v>
+        <v>437.78</v>
       </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I263" s="4" t="inlineStr">
@@ -13966,7 +13966,7 @@
       <c r="J263" s="4" t="inlineStr"/>
       <c r="K263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>621.62</v>
+        <v>746.52</v>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
@@ -14017,7 +14017,7 @@
       <c r="J264" s="2" t="inlineStr"/>
       <c r="K264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14048,7 +14048,7 @@
         </is>
       </c>
       <c r="F265" s="4" t="n">
-        <v>339.46</v>
+        <v>828.76</v>
       </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
       <c r="J265" s="4" t="inlineStr"/>
       <c r="K265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>498.96</v>
+        <v>523.16</v>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       <c r="J266" s="2" t="inlineStr"/>
       <c r="K266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
         </is>
       </c>
       <c r="F267" s="4" t="n">
-        <v>603.0700000000001</v>
+        <v>588.63</v>
       </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I267" s="4" t="inlineStr">
@@ -14170,7 +14170,7 @@
       <c r="J267" s="4" t="inlineStr"/>
       <c r="K267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14201,7 +14201,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>736.65</v>
+        <v>826.6</v>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
@@ -14221,7 +14221,7 @@
       <c r="J268" s="2" t="inlineStr"/>
       <c r="K268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="F269" s="4" t="n">
-        <v>818.85</v>
+        <v>493.64</v>
       </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
       <c r="J269" s="4" t="inlineStr"/>
       <c r="K269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>483.69</v>
+        <v>247.49</v>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
@@ -14323,7 +14323,7 @@
       <c r="J270" s="2" t="inlineStr"/>
       <c r="K270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
         </is>
       </c>
       <c r="F271" s="4" t="n">
-        <v>227.76</v>
+        <v>299.32</v>
       </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
       <c r="J271" s="4" t="inlineStr"/>
       <c r="K271" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>320.99</v>
+        <v>677.87</v>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -14425,7 +14425,7 @@
       <c r="J272" s="2" t="inlineStr"/>
       <c r="K272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="F273" s="4" t="n">
-        <v>768.47</v>
+        <v>846.8</v>
       </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I273" s="4" t="inlineStr">
@@ -14476,7 +14476,7 @@
       <c r="J273" s="4" t="inlineStr"/>
       <c r="K273" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>392.05</v>
+        <v>332.12</v>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
@@ -14527,7 +14527,7 @@
       <c r="J274" s="2" t="inlineStr"/>
       <c r="K274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="F275" s="4" t="n">
-        <v>592.67</v>
+        <v>236.76</v>
       </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr">
@@ -14578,7 +14578,7 @@
       <c r="J275" s="4" t="inlineStr"/>
       <c r="K275" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>741.25</v>
+        <v>298.15</v>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
@@ -14629,7 +14629,7 @@
       <c r="J276" s="2" t="inlineStr"/>
       <c r="K276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="F277" s="4" t="n">
-        <v>364.3</v>
+        <v>928.01</v>
       </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I277" s="4" t="inlineStr">
@@ -14680,7 +14680,7 @@
       <c r="J277" s="4" t="inlineStr"/>
       <c r="K277" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14711,7 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>254.1</v>
+        <v>618.42</v>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
@@ -14731,7 +14731,7 @@
       <c r="J278" s="2" t="inlineStr"/>
       <c r="K278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
         </is>
       </c>
       <c r="F279" s="4" t="n">
-        <v>182.61</v>
+        <v>247.24</v>
       </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr">
@@ -14782,7 +14782,7 @@
       <c r="J279" s="4" t="inlineStr"/>
       <c r="K279" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>448.73</v>
+        <v>691.55</v>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       <c r="J280" s="2" t="inlineStr"/>
       <c r="K280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="F281" s="4" t="n">
-        <v>827.71</v>
+        <v>631.9400000000001</v>
       </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr">
@@ -14884,7 +14884,7 @@
       <c r="J281" s="4" t="inlineStr"/>
       <c r="K281" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14915,7 +14915,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>709.5599999999999</v>
+        <v>653.3200000000001</v>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
@@ -14935,7 +14935,7 @@
       <c r="J282" s="2" t="inlineStr"/>
       <c r="K282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
         </is>
       </c>
       <c r="F283" s="4" t="n">
-        <v>160.98</v>
+        <v>520.14</v>
       </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I283" s="4" t="inlineStr">
@@ -14986,7 +14986,7 @@
       <c r="J283" s="4" t="inlineStr"/>
       <c r="K283" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15017,7 +15017,7 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>326.55</v>
+        <v>302.01</v>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
       <c r="J284" s="2" t="inlineStr"/>
       <c r="K284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="F285" s="4" t="n">
-        <v>451.74</v>
+        <v>610.61</v>
       </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
       <c r="J285" s="4" t="inlineStr"/>
       <c r="K285" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>790.58</v>
+        <v>751.6799999999999</v>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
@@ -15139,7 +15139,7 @@
       <c r="J286" s="2" t="inlineStr"/>
       <c r="K286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="F287" s="4" t="n">
-        <v>674.29</v>
+        <v>624.63</v>
       </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
       </c>
       <c r="H287" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I287" s="4" t="inlineStr">
@@ -15190,7 +15190,7 @@
       <c r="J287" s="4" t="inlineStr"/>
       <c r="K287" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>275.22</v>
+        <v>456.22</v>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
       <c r="J288" s="2" t="inlineStr"/>
       <c r="K288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
         </is>
       </c>
       <c r="F289" s="4" t="n">
-        <v>938.24</v>
+        <v>123.49</v>
       </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr">
@@ -15292,7 +15292,7 @@
       <c r="J289" s="4" t="inlineStr"/>
       <c r="K289" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>774.3099999999999</v>
+        <v>552.77</v>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
       <c r="J290" s="2" t="inlineStr"/>
       <c r="K290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15374,7 +15374,7 @@
         </is>
       </c>
       <c r="F291" s="4" t="n">
-        <v>554.4</v>
+        <v>911.97</v>
       </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>20 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I291" s="4" t="inlineStr">
@@ -15394,7 +15394,7 @@
       <c r="J291" s="4" t="inlineStr"/>
       <c r="K291" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>866.34</v>
+        <v>298.88</v>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
@@ -15445,7 +15445,7 @@
       <c r="J292" s="2" t="inlineStr"/>
       <c r="K292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
         </is>
       </c>
       <c r="F293" s="4" t="n">
-        <v>612.75</v>
+        <v>310.6</v>
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="H293" s="4" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I293" s="4" t="inlineStr">
@@ -15496,7 +15496,7 @@
       <c r="J293" s="4" t="inlineStr"/>
       <c r="K293" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15527,7 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>274.81</v>
+        <v>692.49</v>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
@@ -15547,7 +15547,7 @@
       <c r="J294" s="2" t="inlineStr"/>
       <c r="K294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15578,7 +15578,7 @@
         </is>
       </c>
       <c r="F295" s="4" t="n">
-        <v>172.4</v>
+        <v>814.83</v>
       </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>50 users</t>
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr">
@@ -15598,7 +15598,7 @@
       <c r="J295" s="4" t="inlineStr"/>
       <c r="K295" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15629,7 +15629,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>267.19</v>
+        <v>525.3099999999999</v>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>50 users</t>
+          <t>20 users</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
@@ -15649,7 +15649,7 @@
       <c r="J296" s="2" t="inlineStr"/>
       <c r="K296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
         </is>
       </c>
       <c r="F297" s="4" t="n">
-        <v>444.08</v>
+        <v>559.3200000000001</v>
       </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
       <c r="J297" s="4" t="inlineStr"/>
       <c r="K297" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15731,7 +15731,7 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>932.3</v>
+        <v>467.47</v>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>10 users</t>
+          <t>1 users</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
@@ -15751,7 +15751,7 @@
       <c r="J298" s="2" t="inlineStr"/>
       <c r="K298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
         </is>
       </c>
       <c r="F299" s="4" t="n">
-        <v>944.97</v>
+        <v>472.06</v>
       </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr">
@@ -15802,7 +15802,7 @@
       <c r="J299" s="4" t="inlineStr"/>
       <c r="K299" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>311.89</v>
+        <v>899.0599999999999</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>1 users</t>
+          <t>5 users</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
@@ -15853,7 +15853,7 @@
       <c r="J300" s="2" t="inlineStr"/>
       <c r="K300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="F301" s="4" t="n">
-        <v>256.41</v>
+        <v>829.83</v>
       </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>5 users</t>
+          <t>10 users</t>
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr">
@@ -15904,7 +15904,7 @@
       <c r="J301" s="4" t="inlineStr"/>
       <c r="K301" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:38:38</t>
+          <t>2026-08-01 13:36:49</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-01 09:38:38</t>
+          <t>Generated: 2026-08-01 13:36:50</t>
         </is>
       </c>
     </row>
